--- a/data/externalStats/File1/RPT_RPT3132569263113JV_externalStats.xlsx
+++ b/data/externalStats/File1/RPT_RPT3132569263113JV_externalStats.xlsx
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>5634318.814640129</v>
+        <v>5634318.81464013</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>752.332995</v>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>5231411.651656951</v>
+        <v>5231411.651656952</v>
       </c>
       <c r="AI31" s="56" t="n">
-        <v>780.9839425823877</v>
+        <v>780.9839425823876</v>
       </c>
       <c r="AK31" s="123" t="n">
         <v>7</v>
@@ -2700,7 +2700,7 @@
         <v>2901313.69343935</v>
       </c>
       <c r="AI33" s="56" t="n">
-        <v>354.0840958925123</v>
+        <v>354.0840958925122</v>
       </c>
       <c r="AK33" s="123" t="n">
         <v>9</v>
@@ -3008,7 +3008,7 @@
         <v>1886765.755512452</v>
       </c>
       <c r="AI37" s="56" t="n">
-        <v>432.3470500000001</v>
+        <v>432.34705</v>
       </c>
       <c r="AK37" s="123" t="n">
         <v>13</v>
@@ -3085,7 +3085,7 @@
         <v>1789465.390993749</v>
       </c>
       <c r="AI38" s="56" t="n">
-        <v>2313.128836677756</v>
+        <v>2313.128836677755</v>
       </c>
       <c r="AK38" s="123" t="n">
         <v>14</v>
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="AN41" s="58" t="n">
-        <v>621.5789060000002</v>
+        <v>621.5789060000001</v>
       </c>
     </row>
     <row r="42">
@@ -3756,7 +3756,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>8567448.901922546</v>
+        <v>8567448.901922544</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>10927.29972684575</v>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>3811195.185857767</v>
+        <v>3811195.185857768</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>13941.47613349373</v>
@@ -4001,19 +4001,19 @@
         <v>34482.74630866614</v>
       </c>
       <c r="P54" s="130" t="n">
-        <v>21663.43131355951</v>
+        <v>21663.4313135595</v>
       </c>
       <c r="Q54" s="131" t="n">
         <v>11378.13427675371</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>3423.06153747609</v>
+        <v>3423.061537476089</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T54" s="132" t="n">
-        <v>36464.62712778931</v>
+        <v>36464.6271277893</v>
       </c>
       <c r="V54" s="130" t="n">
         <v>23329.80421791237</v>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>1652160.935343546</v>
+        <v>1652160.935343547</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>5166.812702887033</v>
@@ -4285,7 +4285,7 @@
         <v>855702.5593871593</v>
       </c>
       <c r="AH57" s="56" t="n">
-        <v>2705.748534253711</v>
+        <v>2705.748534253712</v>
       </c>
     </row>
     <row r="58">
@@ -4316,7 +4316,7 @@
         <v>985.1824819707107</v>
       </c>
       <c r="L58" s="131" t="n">
-        <v>255.9237504109173</v>
+        <v>255.9237504109174</v>
       </c>
       <c r="M58" s="131" t="n">
         <v>0</v>
@@ -4328,22 +4328,22 @@
         <v>2524.413145919568</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>955.5306180828586</v>
+        <v>955.5306180828587</v>
       </c>
       <c r="R58" s="131" t="n">
-        <v>249.3743419835244</v>
+        <v>249.3743419835243</v>
       </c>
       <c r="S58" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>3729.318105985952</v>
+        <v>3729.318105985951</v>
       </c>
       <c r="V58" s="130" t="n">
         <v>2449.159189058707</v>
       </c>
       <c r="W58" s="131" t="n">
-        <v>924.0255834445892</v>
+        <v>924.0255834445895</v>
       </c>
       <c r="X58" s="131" t="n">
         <v>242.3455691904668</v>
@@ -4352,7 +4352,7 @@
         <v>0</v>
       </c>
       <c r="Z58" s="132" t="n">
-        <v>3615.530341693763</v>
+        <v>3615.530341693764</v>
       </c>
       <c r="AE58" s="121" t="n">
         <v>10</v>
@@ -4634,19 +4634,19 @@
         <v>350</v>
       </c>
       <c r="J62" s="130" t="n">
-        <v>54.46960886445488</v>
+        <v>54.46960886445489</v>
       </c>
       <c r="K62" s="131" t="n">
-        <v>32.36359794898544</v>
+        <v>32.36359794898545</v>
       </c>
       <c r="L62" s="131" t="n">
-        <v>5.262829051296937</v>
+        <v>5.262829051296938</v>
       </c>
       <c r="M62" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N62" s="132" t="n">
-        <v>92.09603586473726</v>
+        <v>92.09603586473727</v>
       </c>
       <c r="P62" s="130" t="n">
         <v>52.77809362185538</v>
@@ -4655,7 +4655,7 @@
         <v>31.3575465869679</v>
       </c>
       <c r="R62" s="131" t="n">
-        <v>5.099435374751683</v>
+        <v>5.099435374751681</v>
       </c>
       <c r="S62" s="131" t="n">
         <v>0</v>
@@ -4676,7 +4676,7 @@
         <v>0</v>
       </c>
       <c r="Z62" s="132" t="n">
-        <v>86.20104809908413</v>
+        <v>86.20104809908415</v>
       </c>
       <c r="AE62" s="121" t="n">
         <v>14</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>354891.213093305</v>
+        <v>354891.2130933049</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>424.6916390399999</v>
@@ -4715,10 +4715,10 @@
         <v>15424</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>6740.490552500309</v>
+        <v>6740.490552500305</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1724.744513801073</v>
+        <v>1724.744513801075</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>822.9238077059808</v>
@@ -4730,28 +4730,28 @@
         <v>20607.96700619079</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>7085.272226056386</v>
+        <v>7085.272226056382</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>1791.483213016829</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>845.0266611041561</v>
+        <v>845.026661104157</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>12711.55782330638</v>
+        <v>12711.55782330639</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>22433.33992348375</v>
+        <v>22433.33992348376</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>7451.78198484419</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>1871.513247205618</v>
+        <v>1871.513247205616</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>853.5529290622253</v>
+        <v>853.5529290622244</v>
       </c>
       <c r="Y63" s="131" t="n">
         <v>14198.2935037223</v>
@@ -4771,7 +4771,7 @@
         <v>351122.3290545332</v>
       </c>
       <c r="AH63" s="56" t="n">
-        <v>756.0545428044875</v>
+        <v>756.0545428044874</v>
       </c>
     </row>
     <row r="64">
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>243366.9922837368</v>
+        <v>243366.9922837367</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>537.4348217599999</v>
@@ -5126,7 +5126,7 @@
         <v>60611</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>29867.87656926751</v>
+        <v>29867.8765692675</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>13645.46272515257</v>
@@ -5138,10 +5138,10 @@
         <v>11319.80813218343</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>69977.99808268294</v>
+        <v>69977.99808268293</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>31325.89477915732</v>
+        <v>31325.89477915731</v>
       </c>
       <c r="Q68" s="143" t="n">
         <v>14156.50565444037</v>
@@ -5150,7 +5150,7 @@
         <v>4522.561975938522</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>12711.55782330638</v>
+        <v>12711.55782330639</v>
       </c>
       <c r="T68" s="144" t="n">
         <v>75036.73042073625</v>
@@ -5162,13 +5162,13 @@
         <v>14861.92795547624</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>4977.901177068295</v>
+        <v>4977.901177068294</v>
       </c>
       <c r="Y68" s="143" t="n">
         <v>14198.2935037223</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>81093.91498928308</v>
+        <v>81093.91498928305</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -5403,7 +5403,7 @@
         <v>116</v>
       </c>
       <c r="J72" s="130" t="n">
-        <v>69.01858238494688</v>
+        <v>69.0185823849469</v>
       </c>
       <c r="K72" s="131" t="n">
         <v>22.70834769763457</v>
@@ -5540,7 +5540,7 @@
         <v>164.7833881081905</v>
       </c>
       <c r="K74" s="131" t="n">
-        <v>20.95725026267809</v>
+        <v>20.95725026267808</v>
       </c>
       <c r="L74" s="131" t="n">
         <v>0</v>
@@ -5674,7 +5674,7 @@
         <v>122.3822971540443</v>
       </c>
       <c r="K76" s="131" t="n">
-        <v>37.7773142495707</v>
+        <v>37.77731424957069</v>
       </c>
       <c r="L76" s="131" t="n">
         <v>11.60596537795776</v>
@@ -5698,7 +5698,7 @@
         <v>0</v>
       </c>
       <c r="T76" s="132" t="n">
-        <v>171.3618787342558</v>
+        <v>171.3618787342559</v>
       </c>
       <c r="V76" s="130" t="n">
         <v>122.8818745096389</v>
@@ -6006,10 +6006,10 @@
         <v>2517</v>
       </c>
       <c r="J81" s="130" t="n">
-        <v>989.973014341453</v>
+        <v>989.9730143414529</v>
       </c>
       <c r="K81" s="131" t="n">
-        <v>145.811543771265</v>
+        <v>145.8115437712651</v>
       </c>
       <c r="L81" s="131" t="n">
         <v>189.157341959662</v>
@@ -6039,7 +6039,7 @@
         <v>1049.895692388802</v>
       </c>
       <c r="W81" s="131" t="n">
-        <v>137.4499899511355</v>
+        <v>137.4499899511354</v>
       </c>
       <c r="X81" s="131" t="n">
         <v>238.5549502791338</v>
@@ -6623,19 +6623,19 @@
         <v>34590.84721268596</v>
       </c>
       <c r="P90" s="130" t="n">
-        <v>21730.70092040511</v>
+        <v>21730.7009204051</v>
       </c>
       <c r="Q90" s="131" t="n">
         <v>11399.37976868465</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>3439.142351661754</v>
+        <v>3439.142351661753</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T90" s="132" t="n">
-        <v>36569.22304075151</v>
+        <v>36569.2230407515</v>
       </c>
       <c r="V90" s="130" t="n">
         <v>23395.18963672237</v>
@@ -6745,7 +6745,7 @@
         <v>164.7833881081905</v>
       </c>
       <c r="K92" s="131" t="n">
-        <v>20.95725026267809</v>
+        <v>20.95725026267808</v>
       </c>
       <c r="L92" s="131" t="n">
         <v>0</v>
@@ -6876,40 +6876,40 @@
         <v>4251</v>
       </c>
       <c r="J94" s="130" t="n">
-        <v>2717.018167265441</v>
+        <v>2717.018167265442</v>
       </c>
       <c r="K94" s="131" t="n">
         <v>1022.959796220281</v>
       </c>
       <c r="L94" s="131" t="n">
-        <v>267.5297157888751</v>
+        <v>267.5297157888752</v>
       </c>
       <c r="M94" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N94" s="132" t="n">
-        <v>4007.507679274598</v>
+        <v>4007.507679274599</v>
       </c>
       <c r="P94" s="130" t="n">
         <v>2647.540383956738</v>
       </c>
       <c r="Q94" s="131" t="n">
-        <v>992.0443454756096</v>
+        <v>992.0443454756097</v>
       </c>
       <c r="R94" s="131" t="n">
-        <v>261.095255287859</v>
+        <v>261.0952552878589</v>
       </c>
       <c r="S94" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T94" s="132" t="n">
-        <v>3900.679984720207</v>
+        <v>3900.679984720206</v>
       </c>
       <c r="V94" s="130" t="n">
         <v>2572.041063568346</v>
       </c>
       <c r="W94" s="131" t="n">
-        <v>958.767988168246</v>
+        <v>958.7679881682463</v>
       </c>
       <c r="X94" s="131" t="n">
         <v>254.137596261045</v>
@@ -7144,19 +7144,19 @@
         <v>350</v>
       </c>
       <c r="J98" s="130" t="n">
-        <v>54.46960886445488</v>
+        <v>54.46960886445489</v>
       </c>
       <c r="K98" s="131" t="n">
-        <v>32.36359794898544</v>
+        <v>32.36359794898545</v>
       </c>
       <c r="L98" s="131" t="n">
-        <v>5.262829051296937</v>
+        <v>5.262829051296938</v>
       </c>
       <c r="M98" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N98" s="132" t="n">
-        <v>92.09603586473726</v>
+        <v>92.09603586473727</v>
       </c>
       <c r="P98" s="130" t="n">
         <v>52.77809362185538</v>
@@ -7165,7 +7165,7 @@
         <v>31.3575465869679</v>
       </c>
       <c r="R98" s="131" t="n">
-        <v>5.099435374751683</v>
+        <v>5.099435374751681</v>
       </c>
       <c r="S98" s="131" t="n">
         <v>0</v>
@@ -7186,7 +7186,7 @@
         <v>0</v>
       </c>
       <c r="Z98" s="132" t="n">
-        <v>86.20104809908413</v>
+        <v>86.20104809908415</v>
       </c>
     </row>
     <row r="99">
@@ -7211,13 +7211,13 @@
         <v>17941</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>7730.463566841765</v>
+        <v>7730.463566841758</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>1870.556057572341</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>1012.081149665643</v>
+        <v>1012.081149665642</v>
       </c>
       <c r="M99" s="131" t="n">
         <v>12720.84669002336</v>
@@ -7226,7 +7226,7 @@
         <v>23333.9474641031</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>8104.741161981874</v>
+        <v>8104.74116198187</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>1933.712760458118</v>
@@ -7244,16 +7244,16 @@
         <v>8501.677677232994</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>2008.963237156753</v>
+        <v>2008.96323715675</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>1092.107879341358</v>
+        <v>1092.107879341357</v>
       </c>
       <c r="Y99" s="131" t="n">
         <v>15855.13226131755</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>27457.88105504866</v>
+        <v>27457.88105504865</v>
       </c>
     </row>
     <row r="100">
@@ -7562,10 +7562,10 @@
         <v>12720.84669002336</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>74570.62421760744</v>
+        <v>74570.62421760743</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>32705.26137260097</v>
+        <v>32705.26137260096</v>
       </c>
       <c r="Q104" s="143" t="n">
         <v>14376.06408348177</v>
@@ -7577,7 +7577,7 @@
         <v>14213.51337493969</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>79873.18355041168</v>
+        <v>79873.18355041166</v>
       </c>
       <c r="V104" s="142" t="n">
         <v>34693.43084959686</v>
@@ -7586,13 +7586,13 @@
         <v>15071.8596251477</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>5244.063096826499</v>
+        <v>5244.063096826498</v>
       </c>
       <c r="Y104" s="143" t="n">
         <v>15855.13226131755</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>86295.38743677038</v>
+        <v>86295.38743677037</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -8782,7 +8782,7 @@
         <v>15756953.8277056</v>
       </c>
       <c r="AI27" s="56" t="n">
-        <v>1518.116782665446</v>
+        <v>1518.116782665447</v>
       </c>
       <c r="AK27" s="123" t="n">
         <v>3</v>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>5596493.161870112</v>
+        <v>5596493.161870113</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>795.784626769313</v>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>4002229.497978751</v>
+        <v>4002229.49797875</v>
       </c>
       <c r="AI32" s="56" t="n">
-        <v>13973.95203328434</v>
+        <v>13973.95203328433</v>
       </c>
       <c r="AK32" s="123" t="n">
         <v>8</v>
@@ -9301,7 +9301,7 @@
         <v>3129242.204697554</v>
       </c>
       <c r="AI34" s="56" t="n">
-        <v>360.8044705626895</v>
+        <v>360.8044705626896</v>
       </c>
       <c r="AK34" s="123" t="n">
         <v>10</v>
@@ -9455,7 +9455,7 @@
         <v>2065048.249427686</v>
       </c>
       <c r="AI36" s="56" t="n">
-        <v>386.735912532</v>
+        <v>386.7359125319999</v>
       </c>
       <c r="AK36" s="123" t="n">
         <v>12</v>
@@ -9688,7 +9688,7 @@
         </is>
       </c>
       <c r="AN39" s="58" t="n">
-        <v>5364.132132343528</v>
+        <v>5364.132132343529</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" thickBot="1">
@@ -10044,7 +10044,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>874699.7081056555</v>
+        <v>874699.7081056554</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>2206.258066515537</v>
@@ -10221,7 +10221,7 @@
         <v>63080462.99628588</v>
       </c>
       <c r="AH49" s="46" t="n">
-        <v>7316.583474944788</v>
+        <v>7316.583474944789</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" thickBot="1">
@@ -10525,19 +10525,19 @@
         <v>34482.74630866614</v>
       </c>
       <c r="P54" s="130" t="n">
-        <v>21663.43131355951</v>
+        <v>21663.4313135595</v>
       </c>
       <c r="Q54" s="131" t="n">
         <v>11378.13427675371</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>3423.06153747609</v>
+        <v>3423.061537476089</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T54" s="132" t="n">
-        <v>36464.62712778931</v>
+        <v>36464.6271277893</v>
       </c>
       <c r="V54" s="130" t="n">
         <v>23329.80421791237</v>
@@ -10566,7 +10566,7 @@
         <v>1650870.480105934</v>
       </c>
       <c r="AH54" s="56" t="n">
-        <v>4932.34274243002</v>
+        <v>4932.342742430019</v>
       </c>
     </row>
     <row r="55">
@@ -10840,7 +10840,7 @@
         <v>985.1824819707107</v>
       </c>
       <c r="L58" s="131" t="n">
-        <v>255.9237504109173</v>
+        <v>255.9237504109174</v>
       </c>
       <c r="M58" s="131" t="n">
         <v>0</v>
@@ -10852,22 +10852,22 @@
         <v>2524.413145919568</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>955.5306180828586</v>
+        <v>955.5306180828587</v>
       </c>
       <c r="R58" s="131" t="n">
-        <v>249.3743419835244</v>
+        <v>249.3743419835243</v>
       </c>
       <c r="S58" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>3729.318105985952</v>
+        <v>3729.318105985951</v>
       </c>
       <c r="V58" s="130" t="n">
         <v>2449.159189058707</v>
       </c>
       <c r="W58" s="131" t="n">
-        <v>924.0255834445892</v>
+        <v>924.0255834445895</v>
       </c>
       <c r="X58" s="131" t="n">
         <v>242.3455691904668</v>
@@ -10876,7 +10876,7 @@
         <v>0</v>
       </c>
       <c r="Z58" s="132" t="n">
-        <v>3615.530341693763</v>
+        <v>3615.530341693764</v>
       </c>
       <c r="AE58" s="121" t="n">
         <v>10</v>
@@ -10971,7 +10971,7 @@
         <v>454708.4864445277</v>
       </c>
       <c r="AH59" s="56" t="n">
-        <v>2351.277226042233</v>
+        <v>2351.277226042232</v>
       </c>
     </row>
     <row r="60">
@@ -11133,7 +11133,7 @@
         <v>381590.3538050652</v>
       </c>
       <c r="AH61" s="56" t="n">
-        <v>436.4216221102848</v>
+        <v>436.4216221102847</v>
       </c>
     </row>
     <row r="62">
@@ -11158,19 +11158,19 @@
         <v>350</v>
       </c>
       <c r="J62" s="130" t="n">
-        <v>54.46960886445488</v>
+        <v>54.46960886445489</v>
       </c>
       <c r="K62" s="131" t="n">
-        <v>32.36359794898544</v>
+        <v>32.36359794898545</v>
       </c>
       <c r="L62" s="131" t="n">
-        <v>5.262829051296937</v>
+        <v>5.262829051296938</v>
       </c>
       <c r="M62" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N62" s="132" t="n">
-        <v>92.09603586473726</v>
+        <v>92.09603586473727</v>
       </c>
       <c r="P62" s="130" t="n">
         <v>52.77809362185538</v>
@@ -11179,7 +11179,7 @@
         <v>31.3575465869679</v>
       </c>
       <c r="R62" s="131" t="n">
-        <v>5.099435374751683</v>
+        <v>5.099435374751681</v>
       </c>
       <c r="S62" s="131" t="n">
         <v>0</v>
@@ -11200,7 +11200,7 @@
         <v>0</v>
       </c>
       <c r="Z62" s="132" t="n">
-        <v>86.20104809908413</v>
+        <v>86.20104809908415</v>
       </c>
       <c r="AE62" s="121" t="n">
         <v>14</v>
@@ -11239,10 +11239,10 @@
         <v>15424</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>6740.490552500309</v>
+        <v>6740.490552500305</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1724.744513801073</v>
+        <v>1724.744513801075</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>822.9238077059808</v>
@@ -11254,28 +11254,28 @@
         <v>20607.96700619079</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>7085.272226056386</v>
+        <v>7085.272226056382</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>1791.483213016829</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>845.0266611041561</v>
+        <v>845.026661104157</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>12711.55782330638</v>
+        <v>12711.55782330639</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>22433.33992348375</v>
+        <v>22433.33992348376</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>7451.78198484419</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>1871.513247205618</v>
+        <v>1871.513247205616</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>853.5529290622253</v>
+        <v>853.5529290622244</v>
       </c>
       <c r="Y63" s="131" t="n">
         <v>14198.2935037223</v>
@@ -11544,7 +11544,7 @@
         <v>234523.3546800433</v>
       </c>
       <c r="AH66" s="56" t="n">
-        <v>501.3167100144639</v>
+        <v>501.316710014464</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" thickBot="1">
@@ -11650,7 +11650,7 @@
         <v>60611</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>29867.87656926751</v>
+        <v>29867.8765692675</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>13645.46272515257</v>
@@ -11662,10 +11662,10 @@
         <v>11319.80813218343</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>69977.99808268294</v>
+        <v>69977.99808268293</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>31325.89477915732</v>
+        <v>31325.89477915731</v>
       </c>
       <c r="Q68" s="143" t="n">
         <v>14156.50565444037</v>
@@ -11674,7 +11674,7 @@
         <v>4522.561975938522</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>12711.55782330638</v>
+        <v>12711.55782330639</v>
       </c>
       <c r="T68" s="144" t="n">
         <v>75036.73042073625</v>
@@ -11686,13 +11686,13 @@
         <v>14861.92795547624</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>4977.901177068295</v>
+        <v>4977.901177068294</v>
       </c>
       <c r="Y68" s="143" t="n">
         <v>14198.2935037223</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>81093.91498928308</v>
+        <v>81093.91498928305</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -11706,7 +11706,7 @@
         <v>135726.8727122392</v>
       </c>
       <c r="AH68" s="84" t="n">
-        <v>695.3732831631964</v>
+        <v>695.3732831631966</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -11927,7 +11927,7 @@
         <v>116</v>
       </c>
       <c r="J72" s="130" t="n">
-        <v>69.01858238494688</v>
+        <v>69.0185823849469</v>
       </c>
       <c r="K72" s="131" t="n">
         <v>22.70834769763457</v>
@@ -12064,7 +12064,7 @@
         <v>164.7833881081905</v>
       </c>
       <c r="K74" s="131" t="n">
-        <v>20.95725026267809</v>
+        <v>20.95725026267808</v>
       </c>
       <c r="L74" s="131" t="n">
         <v>0</v>
@@ -12198,7 +12198,7 @@
         <v>122.3822971540443</v>
       </c>
       <c r="K76" s="131" t="n">
-        <v>37.7773142495707</v>
+        <v>37.77731424957069</v>
       </c>
       <c r="L76" s="131" t="n">
         <v>11.60596537795776</v>
@@ -12222,7 +12222,7 @@
         <v>0</v>
       </c>
       <c r="T76" s="132" t="n">
-        <v>171.3618787342558</v>
+        <v>171.3618787342559</v>
       </c>
       <c r="V76" s="130" t="n">
         <v>122.8818745096389</v>
@@ -12530,10 +12530,10 @@
         <v>2517</v>
       </c>
       <c r="J81" s="130" t="n">
-        <v>989.973014341453</v>
+        <v>989.9730143414529</v>
       </c>
       <c r="K81" s="131" t="n">
-        <v>145.811543771265</v>
+        <v>145.8115437712651</v>
       </c>
       <c r="L81" s="131" t="n">
         <v>189.157341959662</v>
@@ -12563,7 +12563,7 @@
         <v>1049.895692388802</v>
       </c>
       <c r="W81" s="131" t="n">
-        <v>137.4499899511355</v>
+        <v>137.4499899511354</v>
       </c>
       <c r="X81" s="131" t="n">
         <v>238.5549502791338</v>
@@ -13147,19 +13147,19 @@
         <v>34590.84721268596</v>
       </c>
       <c r="P90" s="130" t="n">
-        <v>21730.70092040511</v>
+        <v>21730.7009204051</v>
       </c>
       <c r="Q90" s="131" t="n">
         <v>11399.37976868465</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>3439.142351661754</v>
+        <v>3439.142351661753</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T90" s="132" t="n">
-        <v>36569.22304075151</v>
+        <v>36569.2230407515</v>
       </c>
       <c r="V90" s="130" t="n">
         <v>23395.18963672237</v>
@@ -13269,7 +13269,7 @@
         <v>164.7833881081905</v>
       </c>
       <c r="K92" s="131" t="n">
-        <v>20.95725026267809</v>
+        <v>20.95725026267808</v>
       </c>
       <c r="L92" s="131" t="n">
         <v>0</v>
@@ -13400,40 +13400,40 @@
         <v>4251</v>
       </c>
       <c r="J94" s="130" t="n">
-        <v>2717.018167265441</v>
+        <v>2717.018167265442</v>
       </c>
       <c r="K94" s="131" t="n">
         <v>1022.959796220281</v>
       </c>
       <c r="L94" s="131" t="n">
-        <v>267.5297157888751</v>
+        <v>267.5297157888752</v>
       </c>
       <c r="M94" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N94" s="132" t="n">
-        <v>4007.507679274598</v>
+        <v>4007.507679274599</v>
       </c>
       <c r="P94" s="130" t="n">
         <v>2647.540383956738</v>
       </c>
       <c r="Q94" s="131" t="n">
-        <v>992.0443454756096</v>
+        <v>992.0443454756097</v>
       </c>
       <c r="R94" s="131" t="n">
-        <v>261.095255287859</v>
+        <v>261.0952552878589</v>
       </c>
       <c r="S94" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T94" s="132" t="n">
-        <v>3900.679984720207</v>
+        <v>3900.679984720206</v>
       </c>
       <c r="V94" s="130" t="n">
         <v>2572.041063568346</v>
       </c>
       <c r="W94" s="131" t="n">
-        <v>958.767988168246</v>
+        <v>958.7679881682463</v>
       </c>
       <c r="X94" s="131" t="n">
         <v>254.137596261045</v>
@@ -13668,19 +13668,19 @@
         <v>350</v>
       </c>
       <c r="J98" s="130" t="n">
-        <v>54.46960886445488</v>
+        <v>54.46960886445489</v>
       </c>
       <c r="K98" s="131" t="n">
-        <v>32.36359794898544</v>
+        <v>32.36359794898545</v>
       </c>
       <c r="L98" s="131" t="n">
-        <v>5.262829051296937</v>
+        <v>5.262829051296938</v>
       </c>
       <c r="M98" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N98" s="132" t="n">
-        <v>92.09603586473726</v>
+        <v>92.09603586473727</v>
       </c>
       <c r="P98" s="130" t="n">
         <v>52.77809362185538</v>
@@ -13689,7 +13689,7 @@
         <v>31.3575465869679</v>
       </c>
       <c r="R98" s="131" t="n">
-        <v>5.099435374751683</v>
+        <v>5.099435374751681</v>
       </c>
       <c r="S98" s="131" t="n">
         <v>0</v>
@@ -13710,7 +13710,7 @@
         <v>0</v>
       </c>
       <c r="Z98" s="132" t="n">
-        <v>86.20104809908413</v>
+        <v>86.20104809908415</v>
       </c>
     </row>
     <row r="99">
@@ -13735,13 +13735,13 @@
         <v>17941</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>7730.463566841765</v>
+        <v>7730.463566841758</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>1870.556057572341</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>1012.081149665643</v>
+        <v>1012.081149665642</v>
       </c>
       <c r="M99" s="131" t="n">
         <v>12720.84669002336</v>
@@ -13750,7 +13750,7 @@
         <v>23333.9474641031</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>8104.741161981874</v>
+        <v>8104.74116198187</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>1933.712760458118</v>
@@ -13768,16 +13768,16 @@
         <v>8501.677677232994</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>2008.963237156753</v>
+        <v>2008.96323715675</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>1092.107879341358</v>
+        <v>1092.107879341357</v>
       </c>
       <c r="Y99" s="131" t="n">
         <v>15855.13226131755</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>27457.88105504866</v>
+        <v>27457.88105504865</v>
       </c>
     </row>
     <row r="100">
@@ -14086,10 +14086,10 @@
         <v>12720.84669002336</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>74570.62421760744</v>
+        <v>74570.62421760743</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>32705.26137260097</v>
+        <v>32705.26137260096</v>
       </c>
       <c r="Q104" s="143" t="n">
         <v>14376.06408348177</v>
@@ -14101,7 +14101,7 @@
         <v>14213.51337493969</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>79873.18355041168</v>
+        <v>79873.18355041166</v>
       </c>
       <c r="V104" s="142" t="n">
         <v>34693.43084959686</v>
@@ -14110,13 +14110,13 @@
         <v>15071.8596251477</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>5244.063096826499</v>
+        <v>5244.063096826498</v>
       </c>
       <c r="Y104" s="143" t="n">
         <v>15855.13226131755</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>86295.38743677038</v>
+        <v>86295.38743677037</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -15149,7 +15149,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>45226804.3126963</v>
+        <v>45226804.31269629</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>57217.44053621583</v>
@@ -15597,10 +15597,10 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>6081004.051788686</v>
+        <v>6081004.051788685</v>
       </c>
       <c r="AI31" s="56" t="n">
-        <v>817.0916674748539</v>
+        <v>817.091667474854</v>
       </c>
       <c r="AK31" s="123" t="n">
         <v>7</v>
@@ -15668,7 +15668,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>4606375.923149249</v>
+        <v>4606375.923149248</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>15724.71578175682</v>
@@ -15822,10 +15822,10 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>3399938.26107962</v>
+        <v>3399938.261079619</v>
       </c>
       <c r="AI34" s="56" t="n">
-        <v>370.475820109104</v>
+        <v>370.4758201091039</v>
       </c>
       <c r="AK34" s="123" t="n">
         <v>10</v>
@@ -15902,7 +15902,7 @@
         <v>2569349.041505356</v>
       </c>
       <c r="AI35" s="56" t="n">
-        <v>2396.746329438651</v>
+        <v>2396.74632943865</v>
       </c>
       <c r="AK35" s="123" t="n">
         <v>11</v>
@@ -15979,7 +15979,7 @@
         <v>2204566.834283146</v>
       </c>
       <c r="AI36" s="56" t="n">
-        <v>397.0037510097246</v>
+        <v>397.0037510097247</v>
       </c>
       <c r="AK36" s="123" t="n">
         <v>12</v>
@@ -16193,10 +16193,10 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>1779292.561884391</v>
+        <v>1779292.56188439</v>
       </c>
       <c r="AI39" s="56" t="n">
-        <v>4040.673218108399</v>
+        <v>4040.673218108398</v>
       </c>
       <c r="AK39" s="123" t="n">
         <v>15</v>
@@ -16263,7 +16263,7 @@
         <v>1737807.438772059</v>
       </c>
       <c r="AI40" s="56" t="n">
-        <v>2131.779535882219</v>
+        <v>2131.779535882218</v>
       </c>
       <c r="AK40" s="123" t="n">
         <v>16</v>
@@ -16587,7 +16587,7 @@
         </is>
       </c>
       <c r="AN44" s="87" t="n">
-        <v>345.0504511449656</v>
+        <v>345.0504511449655</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" thickBot="1">
@@ -17049,19 +17049,19 @@
         <v>34482.74630866614</v>
       </c>
       <c r="P54" s="130" t="n">
-        <v>21663.43131355951</v>
+        <v>21663.4313135595</v>
       </c>
       <c r="Q54" s="131" t="n">
         <v>11378.13427675371</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>3423.06153747609</v>
+        <v>3423.061537476089</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T54" s="132" t="n">
-        <v>36464.62712778931</v>
+        <v>36464.6271277893</v>
       </c>
       <c r="V54" s="130" t="n">
         <v>23329.80421791237</v>
@@ -17090,7 +17090,7 @@
         <v>1842577.455677673</v>
       </c>
       <c r="AH54" s="56" t="n">
-        <v>4337.387620661999</v>
+        <v>4337.387620661998</v>
       </c>
     </row>
     <row r="55">
@@ -17330,10 +17330,10 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>830147.971541152</v>
+        <v>830147.9715411521</v>
       </c>
       <c r="AH57" s="56" t="n">
-        <v>527.7572744857026</v>
+        <v>527.7572744857027</v>
       </c>
     </row>
     <row r="58">
@@ -17364,7 +17364,7 @@
         <v>985.1824819707107</v>
       </c>
       <c r="L58" s="131" t="n">
-        <v>255.9237504109173</v>
+        <v>255.9237504109174</v>
       </c>
       <c r="M58" s="131" t="n">
         <v>0</v>
@@ -17376,22 +17376,22 @@
         <v>2524.413145919568</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>955.5306180828586</v>
+        <v>955.5306180828587</v>
       </c>
       <c r="R58" s="131" t="n">
-        <v>249.3743419835244</v>
+        <v>249.3743419835243</v>
       </c>
       <c r="S58" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>3729.318105985952</v>
+        <v>3729.318105985951</v>
       </c>
       <c r="V58" s="130" t="n">
         <v>2449.159189058707</v>
       </c>
       <c r="W58" s="131" t="n">
-        <v>924.0255834445892</v>
+        <v>924.0255834445895</v>
       </c>
       <c r="X58" s="131" t="n">
         <v>242.3455691904668</v>
@@ -17400,7 +17400,7 @@
         <v>0</v>
       </c>
       <c r="Z58" s="132" t="n">
-        <v>3615.530341693763</v>
+        <v>3615.530341693764</v>
       </c>
       <c r="AE58" s="121" t="n">
         <v>10</v>
@@ -17682,19 +17682,19 @@
         <v>350</v>
       </c>
       <c r="J62" s="130" t="n">
-        <v>54.46960886445488</v>
+        <v>54.46960886445489</v>
       </c>
       <c r="K62" s="131" t="n">
-        <v>32.36359794898544</v>
+        <v>32.36359794898545</v>
       </c>
       <c r="L62" s="131" t="n">
-        <v>5.262829051296937</v>
+        <v>5.262829051296938</v>
       </c>
       <c r="M62" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N62" s="132" t="n">
-        <v>92.09603586473726</v>
+        <v>92.09603586473727</v>
       </c>
       <c r="P62" s="130" t="n">
         <v>52.77809362185538</v>
@@ -17703,7 +17703,7 @@
         <v>31.3575465869679</v>
       </c>
       <c r="R62" s="131" t="n">
-        <v>5.099435374751683</v>
+        <v>5.099435374751681</v>
       </c>
       <c r="S62" s="131" t="n">
         <v>0</v>
@@ -17724,7 +17724,7 @@
         <v>0</v>
       </c>
       <c r="Z62" s="132" t="n">
-        <v>86.20104809908413</v>
+        <v>86.20104809908415</v>
       </c>
       <c r="AE62" s="121" t="n">
         <v>14</v>
@@ -17763,10 +17763,10 @@
         <v>15424</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>6740.490552500309</v>
+        <v>6740.490552500305</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1724.744513801073</v>
+        <v>1724.744513801075</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>822.9238077059808</v>
@@ -17778,28 +17778,28 @@
         <v>20607.96700619079</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>7085.272226056386</v>
+        <v>7085.272226056382</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>1791.483213016829</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>845.0266611041561</v>
+        <v>845.026661104157</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>12711.55782330638</v>
+        <v>12711.55782330639</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>22433.33992348375</v>
+        <v>22433.33992348376</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>7451.78198484419</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>1871.513247205618</v>
+        <v>1871.513247205616</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>853.5529290622253</v>
+        <v>853.5529290622244</v>
       </c>
       <c r="Y63" s="131" t="n">
         <v>14198.2935037223</v>
@@ -17816,7 +17816,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>381241.1667653402</v>
+        <v>381241.1667653401</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>750.0184370681948</v>
@@ -18065,7 +18065,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>234940.361415737</v>
+        <v>234940.3614157371</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>70.89009571611402</v>
@@ -18174,7 +18174,7 @@
         <v>60611</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>29867.87656926751</v>
+        <v>29867.8765692675</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>13645.46272515257</v>
@@ -18186,10 +18186,10 @@
         <v>11319.80813218343</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>69977.99808268294</v>
+        <v>69977.99808268293</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>31325.89477915732</v>
+        <v>31325.89477915731</v>
       </c>
       <c r="Q68" s="143" t="n">
         <v>14156.50565444037</v>
@@ -18198,7 +18198,7 @@
         <v>4522.561975938522</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>12711.55782330638</v>
+        <v>12711.55782330639</v>
       </c>
       <c r="T68" s="144" t="n">
         <v>75036.73042073625</v>
@@ -18210,13 +18210,13 @@
         <v>14861.92795547624</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>4977.901177068295</v>
+        <v>4977.901177068294</v>
       </c>
       <c r="Y68" s="143" t="n">
         <v>14198.2935037223</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>81093.91498928308</v>
+        <v>81093.91498928305</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -18451,7 +18451,7 @@
         <v>116</v>
       </c>
       <c r="J72" s="130" t="n">
-        <v>69.01858238494688</v>
+        <v>69.0185823849469</v>
       </c>
       <c r="K72" s="131" t="n">
         <v>22.70834769763457</v>
@@ -18588,7 +18588,7 @@
         <v>164.7833881081905</v>
       </c>
       <c r="K74" s="131" t="n">
-        <v>20.95725026267809</v>
+        <v>20.95725026267808</v>
       </c>
       <c r="L74" s="131" t="n">
         <v>0</v>
@@ -18722,7 +18722,7 @@
         <v>122.3822971540443</v>
       </c>
       <c r="K76" s="131" t="n">
-        <v>37.7773142495707</v>
+        <v>37.77731424957069</v>
       </c>
       <c r="L76" s="131" t="n">
         <v>11.60596537795776</v>
@@ -18746,7 +18746,7 @@
         <v>0</v>
       </c>
       <c r="T76" s="132" t="n">
-        <v>171.3618787342558</v>
+        <v>171.3618787342559</v>
       </c>
       <c r="V76" s="130" t="n">
         <v>122.8818745096389</v>
@@ -19054,10 +19054,10 @@
         <v>2517</v>
       </c>
       <c r="J81" s="130" t="n">
-        <v>989.973014341453</v>
+        <v>989.9730143414529</v>
       </c>
       <c r="K81" s="131" t="n">
-        <v>145.811543771265</v>
+        <v>145.8115437712651</v>
       </c>
       <c r="L81" s="131" t="n">
         <v>189.157341959662</v>
@@ -19087,7 +19087,7 @@
         <v>1049.895692388802</v>
       </c>
       <c r="W81" s="131" t="n">
-        <v>137.4499899511355</v>
+        <v>137.4499899511354</v>
       </c>
       <c r="X81" s="131" t="n">
         <v>238.5549502791338</v>
@@ -19671,19 +19671,19 @@
         <v>34590.84721268596</v>
       </c>
       <c r="P90" s="130" t="n">
-        <v>21730.70092040511</v>
+        <v>21730.7009204051</v>
       </c>
       <c r="Q90" s="131" t="n">
         <v>11399.37976868465</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>3439.142351661754</v>
+        <v>3439.142351661753</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T90" s="132" t="n">
-        <v>36569.22304075151</v>
+        <v>36569.2230407515</v>
       </c>
       <c r="V90" s="130" t="n">
         <v>23395.18963672237</v>
@@ -19793,7 +19793,7 @@
         <v>164.7833881081905</v>
       </c>
       <c r="K92" s="131" t="n">
-        <v>20.95725026267809</v>
+        <v>20.95725026267808</v>
       </c>
       <c r="L92" s="131" t="n">
         <v>0</v>
@@ -19924,40 +19924,40 @@
         <v>4251</v>
       </c>
       <c r="J94" s="130" t="n">
-        <v>2717.018167265441</v>
+        <v>2717.018167265442</v>
       </c>
       <c r="K94" s="131" t="n">
         <v>1022.959796220281</v>
       </c>
       <c r="L94" s="131" t="n">
-        <v>267.5297157888751</v>
+        <v>267.5297157888752</v>
       </c>
       <c r="M94" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N94" s="132" t="n">
-        <v>4007.507679274598</v>
+        <v>4007.507679274599</v>
       </c>
       <c r="P94" s="130" t="n">
         <v>2647.540383956738</v>
       </c>
       <c r="Q94" s="131" t="n">
-        <v>992.0443454756096</v>
+        <v>992.0443454756097</v>
       </c>
       <c r="R94" s="131" t="n">
-        <v>261.095255287859</v>
+        <v>261.0952552878589</v>
       </c>
       <c r="S94" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T94" s="132" t="n">
-        <v>3900.679984720207</v>
+        <v>3900.679984720206</v>
       </c>
       <c r="V94" s="130" t="n">
         <v>2572.041063568346</v>
       </c>
       <c r="W94" s="131" t="n">
-        <v>958.767988168246</v>
+        <v>958.7679881682463</v>
       </c>
       <c r="X94" s="131" t="n">
         <v>254.137596261045</v>
@@ -20192,19 +20192,19 @@
         <v>350</v>
       </c>
       <c r="J98" s="130" t="n">
-        <v>54.46960886445488</v>
+        <v>54.46960886445489</v>
       </c>
       <c r="K98" s="131" t="n">
-        <v>32.36359794898544</v>
+        <v>32.36359794898545</v>
       </c>
       <c r="L98" s="131" t="n">
-        <v>5.262829051296937</v>
+        <v>5.262829051296938</v>
       </c>
       <c r="M98" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N98" s="132" t="n">
-        <v>92.09603586473726</v>
+        <v>92.09603586473727</v>
       </c>
       <c r="P98" s="130" t="n">
         <v>52.77809362185538</v>
@@ -20213,7 +20213,7 @@
         <v>31.3575465869679</v>
       </c>
       <c r="R98" s="131" t="n">
-        <v>5.099435374751683</v>
+        <v>5.099435374751681</v>
       </c>
       <c r="S98" s="131" t="n">
         <v>0</v>
@@ -20234,7 +20234,7 @@
         <v>0</v>
       </c>
       <c r="Z98" s="132" t="n">
-        <v>86.20104809908413</v>
+        <v>86.20104809908415</v>
       </c>
     </row>
     <row r="99">
@@ -20259,13 +20259,13 @@
         <v>17941</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>7730.463566841765</v>
+        <v>7730.463566841758</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>1870.556057572341</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>1012.081149665643</v>
+        <v>1012.081149665642</v>
       </c>
       <c r="M99" s="131" t="n">
         <v>12720.84669002336</v>
@@ -20274,7 +20274,7 @@
         <v>23333.9474641031</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>8104.741161981874</v>
+        <v>8104.74116198187</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>1933.712760458118</v>
@@ -20292,16 +20292,16 @@
         <v>8501.677677232994</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>2008.963237156753</v>
+        <v>2008.96323715675</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>1092.107879341358</v>
+        <v>1092.107879341357</v>
       </c>
       <c r="Y99" s="131" t="n">
         <v>15855.13226131755</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>27457.88105504866</v>
+        <v>27457.88105504865</v>
       </c>
     </row>
     <row r="100">
@@ -20610,10 +20610,10 @@
         <v>12720.84669002336</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>74570.62421760744</v>
+        <v>74570.62421760743</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>32705.26137260097</v>
+        <v>32705.26137260096</v>
       </c>
       <c r="Q104" s="143" t="n">
         <v>14376.06408348177</v>
@@ -20625,7 +20625,7 @@
         <v>14213.51337493969</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>79873.18355041168</v>
+        <v>79873.18355041166</v>
       </c>
       <c r="V104" s="142" t="n">
         <v>34693.43084959686</v>
@@ -20634,13 +20634,13 @@
         <v>15071.8596251477</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>5244.063096826499</v>
+        <v>5244.063096826498</v>
       </c>
       <c r="Y104" s="143" t="n">
         <v>15855.13226131755</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>86295.38743677038</v>
+        <v>86295.38743677037</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -21673,10 +21673,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>55708663.09676259</v>
+        <v>55708663.09676258</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>68660.92484379247</v>
+        <v>68660.92484379245</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -21830,7 +21830,7 @@
         <v>16867779.98879155</v>
       </c>
       <c r="AI27" s="56" t="n">
-        <v>1589.450980859626</v>
+        <v>1589.450980859627</v>
       </c>
       <c r="AK27" s="123" t="n">
         <v>3</v>
@@ -21907,7 +21907,7 @@
         <v>15283848.85315516</v>
       </c>
       <c r="AI28" s="56" t="n">
-        <v>948.8150981136531</v>
+        <v>948.815098113653</v>
       </c>
       <c r="AK28" s="123" t="n">
         <v>4</v>
@@ -22058,7 +22058,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>11120783.40219731</v>
+        <v>11120783.4021973</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>13115.78537471264</v>
@@ -22124,7 +22124,7 @@
         <v>6528556.355378517</v>
       </c>
       <c r="AI31" s="56" t="n">
-        <v>833.5527624453041</v>
+        <v>833.552762445304</v>
       </c>
       <c r="AK31" s="123" t="n">
         <v>7</v>
@@ -22192,10 +22192,10 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>5251571.184787283</v>
+        <v>5251571.184787281</v>
       </c>
       <c r="AI32" s="56" t="n">
-        <v>17641.43818058407</v>
+        <v>17641.43818058408</v>
       </c>
       <c r="AK32" s="123" t="n">
         <v>8</v>
@@ -22580,7 +22580,7 @@
         <v>2176193.366213972</v>
       </c>
       <c r="AI37" s="56" t="n">
-        <v>4767.99439736791</v>
+        <v>4767.994397367911</v>
       </c>
       <c r="AK37" s="123" t="n">
         <v>13</v>
@@ -22720,7 +22720,7 @@
         <v>2006758.971569033</v>
       </c>
       <c r="AI39" s="56" t="n">
-        <v>3570.123843302601</v>
+        <v>3570.123843302602</v>
       </c>
       <c r="AK39" s="123" t="n">
         <v>15</v>
@@ -23015,7 +23015,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>1209246.390037417</v>
+        <v>1209246.390037416</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>1182.728456312894</v>
@@ -23269,7 +23269,7 @@
         <v>84909330.45760091</v>
       </c>
       <c r="AH49" s="46" t="n">
-        <v>8578.612891536097</v>
+        <v>8578.612891536095</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" thickBot="1">
@@ -23573,19 +23573,19 @@
         <v>34482.74630866614</v>
       </c>
       <c r="P54" s="130" t="n">
-        <v>21663.43131355951</v>
+        <v>21663.4313135595</v>
       </c>
       <c r="Q54" s="131" t="n">
         <v>11378.13427675371</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>3423.06153747609</v>
+        <v>3423.061537476089</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T54" s="132" t="n">
-        <v>36464.62712778931</v>
+        <v>36464.6271277893</v>
       </c>
       <c r="V54" s="130" t="n">
         <v>23329.80421791237</v>
@@ -23614,7 +23614,7 @@
         <v>2255994.565201132</v>
       </c>
       <c r="AH54" s="56" t="n">
-        <v>5118.117392381158</v>
+        <v>5118.117392381159</v>
       </c>
     </row>
     <row r="55">
@@ -23695,7 +23695,7 @@
         <v>1645939.729946921</v>
       </c>
       <c r="AH55" s="56" t="n">
-        <v>4488.014268232506</v>
+        <v>4488.014268232505</v>
       </c>
     </row>
     <row r="56">
@@ -23888,7 +23888,7 @@
         <v>985.1824819707107</v>
       </c>
       <c r="L58" s="131" t="n">
-        <v>255.9237504109173</v>
+        <v>255.9237504109174</v>
       </c>
       <c r="M58" s="131" t="n">
         <v>0</v>
@@ -23900,22 +23900,22 @@
         <v>2524.413145919568</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>955.5306180828586</v>
+        <v>955.5306180828587</v>
       </c>
       <c r="R58" s="131" t="n">
-        <v>249.3743419835244</v>
+        <v>249.3743419835243</v>
       </c>
       <c r="S58" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>3729.318105985952</v>
+        <v>3729.318105985951</v>
       </c>
       <c r="V58" s="130" t="n">
         <v>2449.159189058707</v>
       </c>
       <c r="W58" s="131" t="n">
-        <v>924.0255834445892</v>
+        <v>924.0255834445895</v>
       </c>
       <c r="X58" s="131" t="n">
         <v>242.3455691904668</v>
@@ -23924,7 +23924,7 @@
         <v>0</v>
       </c>
       <c r="Z58" s="132" t="n">
-        <v>3615.530341693763</v>
+        <v>3615.530341693764</v>
       </c>
       <c r="AE58" s="121" t="n">
         <v>10</v>
@@ -24206,19 +24206,19 @@
         <v>350</v>
       </c>
       <c r="J62" s="130" t="n">
-        <v>54.46960886445488</v>
+        <v>54.46960886445489</v>
       </c>
       <c r="K62" s="131" t="n">
-        <v>32.36359794898544</v>
+        <v>32.36359794898545</v>
       </c>
       <c r="L62" s="131" t="n">
-        <v>5.262829051296937</v>
+        <v>5.262829051296938</v>
       </c>
       <c r="M62" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N62" s="132" t="n">
-        <v>92.09603586473726</v>
+        <v>92.09603586473727</v>
       </c>
       <c r="P62" s="130" t="n">
         <v>52.77809362185538</v>
@@ -24227,7 +24227,7 @@
         <v>31.3575465869679</v>
       </c>
       <c r="R62" s="131" t="n">
-        <v>5.099435374751683</v>
+        <v>5.099435374751681</v>
       </c>
       <c r="S62" s="131" t="n">
         <v>0</v>
@@ -24248,7 +24248,7 @@
         <v>0</v>
       </c>
       <c r="Z62" s="132" t="n">
-        <v>86.20104809908413</v>
+        <v>86.20104809908415</v>
       </c>
       <c r="AE62" s="121" t="n">
         <v>14</v>
@@ -24287,10 +24287,10 @@
         <v>15424</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>6740.490552500309</v>
+        <v>6740.490552500305</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1724.744513801073</v>
+        <v>1724.744513801075</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>822.9238077059808</v>
@@ -24302,28 +24302,28 @@
         <v>20607.96700619079</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>7085.272226056386</v>
+        <v>7085.272226056382</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>1791.483213016829</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>845.0266611041561</v>
+        <v>845.026661104157</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>12711.55782330638</v>
+        <v>12711.55782330639</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>22433.33992348375</v>
+        <v>22433.33992348376</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>7451.78198484419</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>1871.513247205618</v>
+        <v>1871.513247205616</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>853.5529290622253</v>
+        <v>853.5529290622244</v>
       </c>
       <c r="Y63" s="131" t="n">
         <v>14198.2935037223</v>
@@ -24698,7 +24698,7 @@
         <v>60611</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>29867.87656926751</v>
+        <v>29867.8765692675</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>13645.46272515257</v>
@@ -24710,10 +24710,10 @@
         <v>11319.80813218343</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>69977.99808268294</v>
+        <v>69977.99808268293</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>31325.89477915732</v>
+        <v>31325.89477915731</v>
       </c>
       <c r="Q68" s="143" t="n">
         <v>14156.50565444037</v>
@@ -24722,7 +24722,7 @@
         <v>4522.561975938522</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>12711.55782330638</v>
+        <v>12711.55782330639</v>
       </c>
       <c r="T68" s="144" t="n">
         <v>75036.73042073625</v>
@@ -24734,13 +24734,13 @@
         <v>14861.92795547624</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>4977.901177068295</v>
+        <v>4977.901177068294</v>
       </c>
       <c r="Y68" s="143" t="n">
         <v>14198.2935037223</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>81093.91498928308</v>
+        <v>81093.91498928305</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -24975,7 +24975,7 @@
         <v>116</v>
       </c>
       <c r="J72" s="130" t="n">
-        <v>69.01858238494688</v>
+        <v>69.0185823849469</v>
       </c>
       <c r="K72" s="131" t="n">
         <v>22.70834769763457</v>
@@ -25112,7 +25112,7 @@
         <v>164.7833881081905</v>
       </c>
       <c r="K74" s="131" t="n">
-        <v>20.95725026267809</v>
+        <v>20.95725026267808</v>
       </c>
       <c r="L74" s="131" t="n">
         <v>0</v>
@@ -25246,7 +25246,7 @@
         <v>122.3822971540443</v>
       </c>
       <c r="K76" s="131" t="n">
-        <v>37.7773142495707</v>
+        <v>37.77731424957069</v>
       </c>
       <c r="L76" s="131" t="n">
         <v>11.60596537795776</v>
@@ -25270,7 +25270,7 @@
         <v>0</v>
       </c>
       <c r="T76" s="132" t="n">
-        <v>171.3618787342558</v>
+        <v>171.3618787342559</v>
       </c>
       <c r="V76" s="130" t="n">
         <v>122.8818745096389</v>
@@ -25578,10 +25578,10 @@
         <v>2517</v>
       </c>
       <c r="J81" s="130" t="n">
-        <v>989.973014341453</v>
+        <v>989.9730143414529</v>
       </c>
       <c r="K81" s="131" t="n">
-        <v>145.811543771265</v>
+        <v>145.8115437712651</v>
       </c>
       <c r="L81" s="131" t="n">
         <v>189.157341959662</v>
@@ -25611,7 +25611,7 @@
         <v>1049.895692388802</v>
       </c>
       <c r="W81" s="131" t="n">
-        <v>137.4499899511355</v>
+        <v>137.4499899511354</v>
       </c>
       <c r="X81" s="131" t="n">
         <v>238.5549502791338</v>
@@ -26195,19 +26195,19 @@
         <v>34590.84721268596</v>
       </c>
       <c r="P90" s="130" t="n">
-        <v>21730.70092040511</v>
+        <v>21730.7009204051</v>
       </c>
       <c r="Q90" s="131" t="n">
         <v>11399.37976868465</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>3439.142351661754</v>
+        <v>3439.142351661753</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T90" s="132" t="n">
-        <v>36569.22304075151</v>
+        <v>36569.2230407515</v>
       </c>
       <c r="V90" s="130" t="n">
         <v>23395.18963672237</v>
@@ -26317,7 +26317,7 @@
         <v>164.7833881081905</v>
       </c>
       <c r="K92" s="131" t="n">
-        <v>20.95725026267809</v>
+        <v>20.95725026267808</v>
       </c>
       <c r="L92" s="131" t="n">
         <v>0</v>
@@ -26448,40 +26448,40 @@
         <v>4251</v>
       </c>
       <c r="J94" s="130" t="n">
-        <v>2717.018167265441</v>
+        <v>2717.018167265442</v>
       </c>
       <c r="K94" s="131" t="n">
         <v>1022.959796220281</v>
       </c>
       <c r="L94" s="131" t="n">
-        <v>267.5297157888751</v>
+        <v>267.5297157888752</v>
       </c>
       <c r="M94" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N94" s="132" t="n">
-        <v>4007.507679274598</v>
+        <v>4007.507679274599</v>
       </c>
       <c r="P94" s="130" t="n">
         <v>2647.540383956738</v>
       </c>
       <c r="Q94" s="131" t="n">
-        <v>992.0443454756096</v>
+        <v>992.0443454756097</v>
       </c>
       <c r="R94" s="131" t="n">
-        <v>261.095255287859</v>
+        <v>261.0952552878589</v>
       </c>
       <c r="S94" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T94" s="132" t="n">
-        <v>3900.679984720207</v>
+        <v>3900.679984720206</v>
       </c>
       <c r="V94" s="130" t="n">
         <v>2572.041063568346</v>
       </c>
       <c r="W94" s="131" t="n">
-        <v>958.767988168246</v>
+        <v>958.7679881682463</v>
       </c>
       <c r="X94" s="131" t="n">
         <v>254.137596261045</v>
@@ -26716,19 +26716,19 @@
         <v>350</v>
       </c>
       <c r="J98" s="130" t="n">
-        <v>54.46960886445488</v>
+        <v>54.46960886445489</v>
       </c>
       <c r="K98" s="131" t="n">
-        <v>32.36359794898544</v>
+        <v>32.36359794898545</v>
       </c>
       <c r="L98" s="131" t="n">
-        <v>5.262829051296937</v>
+        <v>5.262829051296938</v>
       </c>
       <c r="M98" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N98" s="132" t="n">
-        <v>92.09603586473726</v>
+        <v>92.09603586473727</v>
       </c>
       <c r="P98" s="130" t="n">
         <v>52.77809362185538</v>
@@ -26737,7 +26737,7 @@
         <v>31.3575465869679</v>
       </c>
       <c r="R98" s="131" t="n">
-        <v>5.099435374751683</v>
+        <v>5.099435374751681</v>
       </c>
       <c r="S98" s="131" t="n">
         <v>0</v>
@@ -26758,7 +26758,7 @@
         <v>0</v>
       </c>
       <c r="Z98" s="132" t="n">
-        <v>86.20104809908413</v>
+        <v>86.20104809908415</v>
       </c>
     </row>
     <row r="99">
@@ -26783,13 +26783,13 @@
         <v>17941</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>7730.463566841765</v>
+        <v>7730.463566841758</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>1870.556057572341</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>1012.081149665643</v>
+        <v>1012.081149665642</v>
       </c>
       <c r="M99" s="131" t="n">
         <v>12720.84669002336</v>
@@ -26798,7 +26798,7 @@
         <v>23333.9474641031</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>8104.741161981874</v>
+        <v>8104.74116198187</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>1933.712760458118</v>
@@ -26816,16 +26816,16 @@
         <v>8501.677677232994</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>2008.963237156753</v>
+        <v>2008.96323715675</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>1092.107879341358</v>
+        <v>1092.107879341357</v>
       </c>
       <c r="Y99" s="131" t="n">
         <v>15855.13226131755</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>27457.88105504866</v>
+        <v>27457.88105504865</v>
       </c>
     </row>
     <row r="100">
@@ -27134,10 +27134,10 @@
         <v>12720.84669002336</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>74570.62421760744</v>
+        <v>74570.62421760743</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>32705.26137260097</v>
+        <v>32705.26137260096</v>
       </c>
       <c r="Q104" s="143" t="n">
         <v>14376.06408348177</v>
@@ -27149,7 +27149,7 @@
         <v>14213.51337493969</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>79873.18355041168</v>
+        <v>79873.18355041166</v>
       </c>
       <c r="V104" s="142" t="n">
         <v>34693.43084959686</v>
@@ -27158,13 +27158,13 @@
         <v>15071.8596251477</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>5244.063096826499</v>
+        <v>5244.063096826498</v>
       </c>
       <c r="Y104" s="143" t="n">
         <v>15855.13226131755</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>86295.38743677038</v>
+        <v>86295.38743677037</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -28200,7 +28200,7 @@
         <v>69272530.81205235</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>82393.10616487112</v>
+        <v>82393.1061648711</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -28277,7 +28277,7 @@
         <v>30879003.96205981</v>
       </c>
       <c r="AI26" s="56" t="n">
-        <v>2045.210599589361</v>
+        <v>2045.210599589362</v>
       </c>
       <c r="AK26" s="123" t="n">
         <v>2</v>
@@ -28293,7 +28293,7 @@
         </is>
       </c>
       <c r="AN26" s="58" t="n">
-        <v>418.9450962243397</v>
+        <v>418.9450962243398</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" thickBot="1">
@@ -28428,7 +28428,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>17530290.57365696</v>
+        <v>17530290.57365695</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>1621.096949888542</v>
@@ -28505,7 +28505,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>14570481.40100322</v>
+        <v>14570481.40100323</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>1523.105781032218</v>
@@ -28648,7 +28648,7 @@
         <v>7082919.956535397</v>
       </c>
       <c r="AI31" s="56" t="n">
-        <v>850.3564973906489</v>
+        <v>850.356497390649</v>
       </c>
       <c r="AK31" s="123" t="n">
         <v>7</v>
@@ -28947,7 +28947,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>3344521.812389606</v>
+        <v>3344521.812389607</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>2764.898270390802</v>
@@ -29101,10 +29101,10 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>2478636.557893779</v>
+        <v>2478636.55789378</v>
       </c>
       <c r="AI37" s="56" t="n">
-        <v>412.9698158775625</v>
+        <v>412.9698158775626</v>
       </c>
       <c r="AK37" s="123" t="n">
         <v>13</v>
@@ -29244,7 +29244,7 @@
         <v>2260678.222648065</v>
       </c>
       <c r="AI39" s="56" t="n">
-        <v>2957.226786839574</v>
+        <v>2957.226786839573</v>
       </c>
       <c r="AK39" s="123" t="n">
         <v>15</v>
@@ -29404,7 +29404,7 @@
         </is>
       </c>
       <c r="AN41" s="58" t="n">
-        <v>607.204390878412</v>
+        <v>607.2043908784119</v>
       </c>
     </row>
     <row r="42">
@@ -29793,7 +29793,7 @@
         <v>100308104.1568862</v>
       </c>
       <c r="AH49" s="46" t="n">
-        <v>9398.673181966911</v>
+        <v>9398.673181966913</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" thickBot="1">
@@ -30097,19 +30097,19 @@
         <v>34482.74630866614</v>
       </c>
       <c r="P54" s="130" t="n">
-        <v>21663.43131355951</v>
+        <v>21663.4313135595</v>
       </c>
       <c r="Q54" s="131" t="n">
         <v>11378.13427675371</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>3423.06153747609</v>
+        <v>3423.061537476089</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T54" s="132" t="n">
-        <v>36464.62712778931</v>
+        <v>36464.6271277893</v>
       </c>
       <c r="V54" s="130" t="n">
         <v>23329.80421791237</v>
@@ -30412,7 +30412,7 @@
         <v>985.1824819707107</v>
       </c>
       <c r="L58" s="131" t="n">
-        <v>255.9237504109173</v>
+        <v>255.9237504109174</v>
       </c>
       <c r="M58" s="131" t="n">
         <v>0</v>
@@ -30424,22 +30424,22 @@
         <v>2524.413145919568</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>955.5306180828586</v>
+        <v>955.5306180828587</v>
       </c>
       <c r="R58" s="131" t="n">
-        <v>249.3743419835244</v>
+        <v>249.3743419835243</v>
       </c>
       <c r="S58" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>3729.318105985952</v>
+        <v>3729.318105985951</v>
       </c>
       <c r="V58" s="130" t="n">
         <v>2449.159189058707</v>
       </c>
       <c r="W58" s="131" t="n">
-        <v>924.0255834445892</v>
+        <v>924.0255834445895</v>
       </c>
       <c r="X58" s="131" t="n">
         <v>242.3455691904668</v>
@@ -30448,7 +30448,7 @@
         <v>0</v>
       </c>
       <c r="Z58" s="132" t="n">
-        <v>3615.530341693763</v>
+        <v>3615.530341693764</v>
       </c>
       <c r="AE58" s="121" t="n">
         <v>10</v>
@@ -30730,19 +30730,19 @@
         <v>350</v>
       </c>
       <c r="J62" s="130" t="n">
-        <v>54.46960886445488</v>
+        <v>54.46960886445489</v>
       </c>
       <c r="K62" s="131" t="n">
-        <v>32.36359794898544</v>
+        <v>32.36359794898545</v>
       </c>
       <c r="L62" s="131" t="n">
-        <v>5.262829051296937</v>
+        <v>5.262829051296938</v>
       </c>
       <c r="M62" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N62" s="132" t="n">
-        <v>92.09603586473726</v>
+        <v>92.09603586473727</v>
       </c>
       <c r="P62" s="130" t="n">
         <v>52.77809362185538</v>
@@ -30751,7 +30751,7 @@
         <v>31.3575465869679</v>
       </c>
       <c r="R62" s="131" t="n">
-        <v>5.099435374751683</v>
+        <v>5.099435374751681</v>
       </c>
       <c r="S62" s="131" t="n">
         <v>0</v>
@@ -30772,7 +30772,7 @@
         <v>0</v>
       </c>
       <c r="Z62" s="132" t="n">
-        <v>86.20104809908413</v>
+        <v>86.20104809908415</v>
       </c>
       <c r="AE62" s="121" t="n">
         <v>14</v>
@@ -30811,10 +30811,10 @@
         <v>15424</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>6740.490552500309</v>
+        <v>6740.490552500305</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1724.744513801073</v>
+        <v>1724.744513801075</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>822.9238077059808</v>
@@ -30826,28 +30826,28 @@
         <v>20607.96700619079</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>7085.272226056386</v>
+        <v>7085.272226056382</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>1791.483213016829</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>845.0266611041561</v>
+        <v>845.026661104157</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>12711.55782330638</v>
+        <v>12711.55782330639</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>22433.33992348375</v>
+        <v>22433.33992348376</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>7451.78198484419</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>1871.513247205618</v>
+        <v>1871.513247205616</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>853.5529290622253</v>
+        <v>853.5529290622244</v>
       </c>
       <c r="Y63" s="131" t="n">
         <v>14198.2935037223</v>
@@ -31222,7 +31222,7 @@
         <v>60611</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>29867.87656926751</v>
+        <v>29867.8765692675</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>13645.46272515257</v>
@@ -31234,10 +31234,10 @@
         <v>11319.80813218343</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>69977.99808268294</v>
+        <v>69977.99808268293</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>31325.89477915732</v>
+        <v>31325.89477915731</v>
       </c>
       <c r="Q68" s="143" t="n">
         <v>14156.50565444037</v>
@@ -31246,7 +31246,7 @@
         <v>4522.561975938522</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>12711.55782330638</v>
+        <v>12711.55782330639</v>
       </c>
       <c r="T68" s="144" t="n">
         <v>75036.73042073625</v>
@@ -31258,13 +31258,13 @@
         <v>14861.92795547624</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>4977.901177068295</v>
+        <v>4977.901177068294</v>
       </c>
       <c r="Y68" s="143" t="n">
         <v>14198.2935037223</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>81093.91498928308</v>
+        <v>81093.91498928305</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -31278,7 +31278,7 @@
         <v>108436.894998139</v>
       </c>
       <c r="AH68" s="84" t="n">
-        <v>350.0774866281456</v>
+        <v>350.0774866281455</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -31499,7 +31499,7 @@
         <v>116</v>
       </c>
       <c r="J72" s="130" t="n">
-        <v>69.01858238494688</v>
+        <v>69.0185823849469</v>
       </c>
       <c r="K72" s="131" t="n">
         <v>22.70834769763457</v>
@@ -31636,7 +31636,7 @@
         <v>164.7833881081905</v>
       </c>
       <c r="K74" s="131" t="n">
-        <v>20.95725026267809</v>
+        <v>20.95725026267808</v>
       </c>
       <c r="L74" s="131" t="n">
         <v>0</v>
@@ -31770,7 +31770,7 @@
         <v>122.3822971540443</v>
       </c>
       <c r="K76" s="131" t="n">
-        <v>37.7773142495707</v>
+        <v>37.77731424957069</v>
       </c>
       <c r="L76" s="131" t="n">
         <v>11.60596537795776</v>
@@ -31794,7 +31794,7 @@
         <v>0</v>
       </c>
       <c r="T76" s="132" t="n">
-        <v>171.3618787342558</v>
+        <v>171.3618787342559</v>
       </c>
       <c r="V76" s="130" t="n">
         <v>122.8818745096389</v>
@@ -32102,10 +32102,10 @@
         <v>2517</v>
       </c>
       <c r="J81" s="130" t="n">
-        <v>989.973014341453</v>
+        <v>989.9730143414529</v>
       </c>
       <c r="K81" s="131" t="n">
-        <v>145.811543771265</v>
+        <v>145.8115437712651</v>
       </c>
       <c r="L81" s="131" t="n">
         <v>189.157341959662</v>
@@ -32135,7 +32135,7 @@
         <v>1049.895692388802</v>
       </c>
       <c r="W81" s="131" t="n">
-        <v>137.4499899511355</v>
+        <v>137.4499899511354</v>
       </c>
       <c r="X81" s="131" t="n">
         <v>238.5549502791338</v>
@@ -32719,19 +32719,19 @@
         <v>34590.84721268596</v>
       </c>
       <c r="P90" s="130" t="n">
-        <v>21730.70092040511</v>
+        <v>21730.7009204051</v>
       </c>
       <c r="Q90" s="131" t="n">
         <v>11399.37976868465</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>3439.142351661754</v>
+        <v>3439.142351661753</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T90" s="132" t="n">
-        <v>36569.22304075151</v>
+        <v>36569.2230407515</v>
       </c>
       <c r="V90" s="130" t="n">
         <v>23395.18963672237</v>
@@ -32841,7 +32841,7 @@
         <v>164.7833881081905</v>
       </c>
       <c r="K92" s="131" t="n">
-        <v>20.95725026267809</v>
+        <v>20.95725026267808</v>
       </c>
       <c r="L92" s="131" t="n">
         <v>0</v>
@@ -32972,40 +32972,40 @@
         <v>4251</v>
       </c>
       <c r="J94" s="130" t="n">
-        <v>2717.018167265441</v>
+        <v>2717.018167265442</v>
       </c>
       <c r="K94" s="131" t="n">
         <v>1022.959796220281</v>
       </c>
       <c r="L94" s="131" t="n">
-        <v>267.5297157888751</v>
+        <v>267.5297157888752</v>
       </c>
       <c r="M94" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N94" s="132" t="n">
-        <v>4007.507679274598</v>
+        <v>4007.507679274599</v>
       </c>
       <c r="P94" s="130" t="n">
         <v>2647.540383956738</v>
       </c>
       <c r="Q94" s="131" t="n">
-        <v>992.0443454756096</v>
+        <v>992.0443454756097</v>
       </c>
       <c r="R94" s="131" t="n">
-        <v>261.095255287859</v>
+        <v>261.0952552878589</v>
       </c>
       <c r="S94" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T94" s="132" t="n">
-        <v>3900.679984720207</v>
+        <v>3900.679984720206</v>
       </c>
       <c r="V94" s="130" t="n">
         <v>2572.041063568346</v>
       </c>
       <c r="W94" s="131" t="n">
-        <v>958.767988168246</v>
+        <v>958.7679881682463</v>
       </c>
       <c r="X94" s="131" t="n">
         <v>254.137596261045</v>
@@ -33240,19 +33240,19 @@
         <v>350</v>
       </c>
       <c r="J98" s="130" t="n">
-        <v>54.46960886445488</v>
+        <v>54.46960886445489</v>
       </c>
       <c r="K98" s="131" t="n">
-        <v>32.36359794898544</v>
+        <v>32.36359794898545</v>
       </c>
       <c r="L98" s="131" t="n">
-        <v>5.262829051296937</v>
+        <v>5.262829051296938</v>
       </c>
       <c r="M98" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N98" s="132" t="n">
-        <v>92.09603586473726</v>
+        <v>92.09603586473727</v>
       </c>
       <c r="P98" s="130" t="n">
         <v>52.77809362185538</v>
@@ -33261,7 +33261,7 @@
         <v>31.3575465869679</v>
       </c>
       <c r="R98" s="131" t="n">
-        <v>5.099435374751683</v>
+        <v>5.099435374751681</v>
       </c>
       <c r="S98" s="131" t="n">
         <v>0</v>
@@ -33282,7 +33282,7 @@
         <v>0</v>
       </c>
       <c r="Z98" s="132" t="n">
-        <v>86.20104809908413</v>
+        <v>86.20104809908415</v>
       </c>
     </row>
     <row r="99">
@@ -33307,13 +33307,13 @@
         <v>17941</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>7730.463566841765</v>
+        <v>7730.463566841758</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>1870.556057572341</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>1012.081149665643</v>
+        <v>1012.081149665642</v>
       </c>
       <c r="M99" s="131" t="n">
         <v>12720.84669002336</v>
@@ -33322,7 +33322,7 @@
         <v>23333.9474641031</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>8104.741161981874</v>
+        <v>8104.74116198187</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>1933.712760458118</v>
@@ -33340,16 +33340,16 @@
         <v>8501.677677232994</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>2008.963237156753</v>
+        <v>2008.96323715675</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>1092.107879341358</v>
+        <v>1092.107879341357</v>
       </c>
       <c r="Y99" s="131" t="n">
         <v>15855.13226131755</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>27457.88105504866</v>
+        <v>27457.88105504865</v>
       </c>
     </row>
     <row r="100">
@@ -33658,10 +33658,10 @@
         <v>12720.84669002336</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>74570.62421760744</v>
+        <v>74570.62421760743</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>32705.26137260097</v>
+        <v>32705.26137260096</v>
       </c>
       <c r="Q104" s="143" t="n">
         <v>14376.06408348177</v>
@@ -33673,7 +33673,7 @@
         <v>14213.51337493969</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>79873.18355041168</v>
+        <v>79873.18355041166</v>
       </c>
       <c r="V104" s="142" t="n">
         <v>34693.43084959686</v>
@@ -33682,13 +33682,13 @@
         <v>15071.8596251477</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>5244.063096826499</v>
+        <v>5244.063096826498</v>
       </c>
       <c r="Y104" s="143" t="n">
         <v>15855.13226131755</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>86295.38743677038</v>
+        <v>86295.38743677037</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
